--- a/rmonize/data_dictionary/DD_CARLA_P1.xlsx
+++ b/rmonize/data_dictionary/DD_CARLA_P1.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SALT_BISCUIT_0605</t>
+          <t>DOUGH_PASTRY_0606</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Intake of crackers and breadsticks [g/d]</t>
+          <t>Intake of fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DOUGH_PASTRY_0606</t>
+          <t>MEAT_PROD_07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Intake of fine bakery products [g/d]</t>
+          <t>Intake of meat and meat products [g/d]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MEAT_PROD_07</t>
+          <t>RED_MEAT_0701</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Intake of meat and meat products [g/d]</t>
+          <t>Intake of red meat (mammals meat) [g/d]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RED_MEAT_0701</t>
+          <t>BEEF_070101</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
+          <t>Intake of cow, ox or bull fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BEEF_070101</t>
+          <t>VEAL_070102</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Intake of cow, ox or bull fresh meat [g/d]</t>
+          <t>Intake of calf fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VEAL_070102</t>
+          <t>PORK_070103</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Intake of calf fresh meat [g/d]</t>
+          <t>Intake of pig fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PORK_070103</t>
+          <t>POULTRY_0702</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Intake of pig fresh meat [g/d]</t>
+          <t>Intake of poultry meat [g/d]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MUTTON_LAMB_070104</t>
+          <t>OTHERPOULTRY_070200</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Intake of lamb and sheep meat [g/d]</t>
+          <t>Intake of other poultry meat [g/d]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>POULTRY_0702</t>
+          <t>CHICKEN_070201</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Intake of poultry meat [g/d]</t>
+          <t>Intake of chicken meat [g/d]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OTHERPOULTRY_070200</t>
+          <t>PROCMEAT_0704</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Intake of other poultry meat [g/d]</t>
+          <t>Intake of processed or preserved meat [g/d]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CHICKEN_070201</t>
+          <t>OFFALS_0705</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Intake of chicken meat [g/d]</t>
+          <t>Intake of animal offal and other slaughtering [g/d]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RABBIT_070205</t>
+          <t>FISH_SHELLFISH_08</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Intake of rabbit meat [g/d]</t>
+          <t>Intake of fish and seafood and products thereof [g/d]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PROCMEAT_0704</t>
+          <t>FISH_0801</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
+          <t>Intake of fish (meat) [g/d]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OFFALS_0705</t>
+          <t>FISH_PROD_0803</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Intake of animal offal and other slaughtering [g/d]</t>
+          <t>Intake of processed fish [g/d]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FISH_SHELLFISH_08</t>
+          <t>EGG_PROD_09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Intake of fish and seafood and products thereof [g/d]</t>
+          <t>Intake of eggs and egg products [g/d]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FISH_0801</t>
+          <t>EGGS_0901</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Intake of fish (meat) [g/d]</t>
+          <t>Intake of eggs [g/d]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FISH_PROD_0803</t>
+          <t>FAT_10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Intake of processed fish [g/d]</t>
+          <t>Intake of animal and vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EGG_PROD_09</t>
+          <t>VEGOILS_1001</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Intake of eggs and egg products [g/d]</t>
+          <t>Intake of vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EGGS_0901</t>
+          <t>BUTTER_1002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Intake of eggs [g/d]</t>
+          <t>Intake of butter [g/d]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FAT_10</t>
+          <t>MARGARINE_1003</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Intake of animal and vegetable fats and oils [g/d]</t>
+          <t>Intake of margarines and similar [g/d]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VEGOILS_1001</t>
+          <t>FRYFAT_1004</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Intake of vegetable fats and oils [g/d]</t>
+          <t>Intake of blended frying oil/fats [g/d]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BUTTER_1002</t>
+          <t>OTHER_ANIMALFAT_1006</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Intake of butter [g/d]</t>
+          <t>Intake of animal fats (processed fat from animal tissue) [g/d]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARGARINE_1003</t>
+          <t>SUGAR_CONFECT_11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Intake of margarines and similar [g/d]</t>
+          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRYFAT_1004</t>
+          <t>HONEY_JAM_1101</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Intake of blended frying oil/fats [g/d]</t>
+          <t>Intake of sugars, syrups, honey and table-top sweeteners [g/d]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OTHER_ANIMALFAT_1006</t>
+          <t>CHOCOLATE_1102</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Intake of animal fats (processed fat from animal tissue) [g/d]</t>
+          <t>Intake of chocolate, chocolate products and chocolate coated confectionary [g/d]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
+          <t>NONCHOC_SWEETS_1103</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
+          <t>Intake of sweet bars and other formed sweet masses, candies (soft and hard) and other confectionery including breath refreshening microsweets [g/d]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HONEY_JAM_1101</t>
+          <t>ICECREAM_1105</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Intake of sugars, syrups, honey and table-top sweeteners [g/d]</t>
+          <t>Intake of spoonable desserts and ice creams [g/d]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CHOCOLATE_1102</t>
+          <t>ICECREAM_MILK_110501</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Intake of chocolate, chocolate products and chocolate coated confectionary [g/d]</t>
+          <t>Intake of milk-based ice cream [g/d]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NONCHOC_SWEETS_1103</t>
+          <t>CAKES_12</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Intake of sweet bars and other formed sweet masses, candies (soft and hard) and other confectionery including breath refreshening microsweets [g/d]</t>
+          <t>Intake of cakes and fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ICECREAM_1105</t>
+          <t>VARPASTRY_1201</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Intake of spoonable desserts and ice creams [g/d]</t>
+          <t>Intake of various pastry [g/d]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ICECREAM_MILK_110501</t>
+          <t>DRYCAKE_1202</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Intake of milk-based ice cream [g/d]</t>
+          <t>Intake of sponge biscuits and plain cakes [g/d]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
+          <t>NONALC_BEV_13</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
+          <t>Intake of non-alcoholic beverages [g/d]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VARPASTRY_1201</t>
+          <t>FRUITVEG_JUICE_1301</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Intake of various pastry [g/d]</t>
+          <t>Intake of fruit and vegetable juices [g/d]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DRYCAKE_1202</t>
+          <t>SOFTDRINKS_1302</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Intake of sponge biscuits and plain cakes [g/d]</t>
+          <t>Intake of soft drinks [g/d]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NONALC_BEV_13</t>
+          <t>HOTDRINKS_1303</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Intake of non-alcoholic beverages [g/d]</t>
+          <t>Intake of hot drinks and similar (coffee, cocoa, tea and herbal infusions) [g/d]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
+          <t>COFFEE_130301</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
+          <t>Coffee intake [g/d]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
+          <t>TEA_130302</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Intake of soft drinks [g/d]</t>
+          <t>Tea intake [g/d]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HOTDRINKS_1303</t>
+          <t>HERBALTEA_130303</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Intake of hot drinks and similar (coffee, cocoa, tea and herbal infusions) [g/d]</t>
+          <t>Intake of herbal and other non-tea infusions [g/d]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COFFEE_130301</t>
+          <t>WATER_1304</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Coffee intake [g/d]</t>
+          <t>Intake of water and water-based beverages [g/d]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TEA_130302</t>
+          <t>ALC_BEV_14</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tea intake [g/d]</t>
+          <t>Alcoholic beverage intake [g/d]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HERBALTEA_130303</t>
+          <t>WINE_1401</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Intake of herbal and other non-tea infusions [g/d]</t>
+          <t>Intake of wine and wine-like drinks [g/d]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COFFEE_IMITATE_130304</t>
+          <t>FORTWINE_1402</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Intake of chicory coffee infusion and coffee imitate beverages [g/d]</t>
+          <t>Intake of fortified/liqueur wine [g/d]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WATER_1304</t>
+          <t>BEER_1403</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Intake of water and water-based beverages [g/d]</t>
+          <t>Intake of beer and beer-like beverage [g/d]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ALC_BEV_14</t>
+          <t>SPIRITS_1404</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Alcoholic beverage intake [g/d]</t>
+          <t>Intake of unsweetened spirits [g/d]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WINE_1401</t>
+          <t>HERBLIQUEUR_1405</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Intake of wine and wine-like drinks [g/d]</t>
+          <t>Intake of herb liqueur [g/d]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FORTWINE_1402</t>
+          <t>LIQUEURS_1406</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Intake of fortified/liqueur wine [g/d]</t>
+          <t>Intake of liqueurs [g/d]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BEER_1403</t>
+          <t>CONDIMENT_SAUCES_15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Intake of beer and beer-like beverage [g/d]</t>
+          <t>Intake of seasoning, sauces and condiments [g/d]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SPIRITS_1404</t>
+          <t>SAUCES_1501</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Intake of unsweetened spirits [g/d]</t>
+          <t>Intake of savoury sauces [g/d]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HERBLIQUEUR_1405</t>
+          <t>TOMATOSAUCE_150101</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Intake of herb liqueur [g/d]</t>
+          <t>Intake of tomato-containing cooked sauces [g/d]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LIQUEURS_1406</t>
+          <t>DRESSINGS_150102</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Intake of liqueurs [g/d]</t>
+          <t>Dressing intake [g/d]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CONDIMENT_SAUCES_15</t>
+          <t>MAYONNAISE_150103</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Intake of seasoning, sauces and condiments [g/d]</t>
+          <t>Intake of mayonnaise [g/d]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAUCES_1501</t>
+          <t>HERBS_SPICES_1503</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Intake of savoury sauces [g/d]</t>
+          <t>Intakes of berbs, spices and similar [g/d]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOMATOSAUCE_150101</t>
+          <t>SOUP_BOUILLON_16</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Intake of tomato-containing cooked sauces [g/d]</t>
+          <t>Intake of soups and broths [g/d]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DRESSINGS_150102</t>
+          <t>SOUP_1601</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dressing intake [g/d]</t>
+          <t>Intake of soups [g/d]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAYONNAISE_150103</t>
+          <t>BOUILLON_1602</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Intake of mayonnaise [g/d]</t>
+          <t>Intake of mixed vegetables soup, clear meat soup [g/d]</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HERBS_SPICES_1503</t>
+          <t>MISCELLANEOUS_17</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Intakes of berbs, spices and similar [g/d]</t>
+          <t>Intake of miscellaneous [g/d]</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CONDIMENTS_1504</t>
+          <t>VEG_DISHES_1700</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Condiments intake [g/d]</t>
+          <t>Intake of vegetarian products and dishes [g/d]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SOUP_BOUILLON_16</t>
+          <t>SOY_PROD_1701</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Intake of soups and broths [g/d]</t>
+          <t>Intake of soy products [g/d]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SOUP_1601</t>
+          <t>DIET_PROD_1702</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Intake of soups [g/d]</t>
+          <t>Intake of food for weight reduction [g/d]</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2443,115 +2443,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BOUILLON_1602</t>
+          <t>ART_SWEETENER_170201</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Intake of mixed vegetables soup, clear meat soup [g/d]</t>
+          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>MISCELLANEOUS_17</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Intake of miscellaneous [g/d]</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>VEG_DISHES_1700</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Intake of vegetarian products and dishes [g/d]</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>SOY_PROD_1701</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Intake of soy products [g/d]</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>DIET_PROD_1702</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Intake of food for weight reduction [g/d]</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>ART_SWEETENER_170201</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
